--- a/artfynd/A 43194-2022 artfynd.xlsx
+++ b/artfynd/A 43194-2022 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 43194-2022 artfynd.xlsx
+++ b/artfynd/A 43194-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY20"/>
+  <dimension ref="A1:AY21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2849,6 +2849,129 @@
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>114896993</v>
+      </c>
+      <c r="B21" t="n">
+        <v>57257</v>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>100110</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Gråspett</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Picus canus</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>J.F. Gmelin, 1788</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="K21" t="inlineStr"/>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>Bengtmyren (Sakrisbodarna, Ås), Jmt</t>
+        </is>
+      </c>
+      <c r="Q21" t="n">
+        <v>478238</v>
+      </c>
+      <c r="R21" t="n">
+        <v>7019756</v>
+      </c>
+      <c r="S21" t="n">
+        <v>50</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Ås</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>2024-02-27</t>
+        </is>
+      </c>
+      <c r="Z21" t="inlineStr">
+        <is>
+          <t>12:01</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>2024-02-27</t>
+        </is>
+      </c>
+      <c r="AB21" t="inlineStr">
+        <is>
+          <t>12:01</t>
+        </is>
+      </c>
+      <c r="AD21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT21" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>Kristofer Holmsten</t>
+        </is>
+      </c>
+      <c r="AX21" t="inlineStr">
+        <is>
+          <t>Kristofer Holmsten</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 43194-2022 artfynd.xlsx
+++ b/artfynd/A 43194-2022 artfynd.xlsx
@@ -2854,7 +2854,7 @@
         <v>114896993</v>
       </c>
       <c r="B21" t="n">
-        <v>57499</v>
+        <v>57502</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
